--- a/monthly_budget.xlsx
+++ b/monthly_budget.xlsx
@@ -453,7 +453,7 @@
         <v>6</v>
       </c>
       <c r="D2" s="3">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>7</v>

--- a/monthly_budget.xlsx
+++ b/monthly_budget.xlsx
@@ -453,7 +453,7 @@
         <v>6</v>
       </c>
       <c r="D2" s="3">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>7</v>
